--- a/resource/专业分类.xlsx
+++ b/resource/专业分类.xlsx
@@ -5,28 +5,36 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\RustProject\aios_workspace\aios-database\resource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A079A9-3130-4C74-B59B-3AD11E7E688A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F389534-859C-4286-A17F-0C1E3B1E5473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8520" yWindow="780" windowWidth="16780" windowHeight="14230" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="109">
   <si>
     <t>PIPE</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -373,6 +381,94 @@
   </si>
   <si>
     <t>电气照明管线</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>V</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>W</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>T</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>辐射安全</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>反应堆热工水力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>辐射监测</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>建筑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>J</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>结构</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>N</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暖通</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>给排水</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>照明</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -416,13 +512,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1173,7 +1275,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CE6209C-C647-4AE3-9980-4524CAC659D9}">
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.5" customWidth="1"/>
@@ -1183,129 +1285,129 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="21.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="C2" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="2" t="s">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="2" t="s">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="1" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="1" t="s">
+      <c r="A5" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="C5" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="1" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="2" t="s">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="1" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="2" t="s">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="1" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="1" t="s">
+      <c r="A8" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="5" t="s">
         <v>81</v>
       </c>
       <c r="D8" t="s">
@@ -1319,9 +1421,9 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
       <c r="D9" t="s">
         <v>32</v>
       </c>
@@ -1333,9 +1435,9 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
       <c r="D10" t="s">
         <v>34</v>
       </c>
@@ -1347,9 +1449,9 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
       <c r="D11" t="s">
         <v>36</v>
       </c>
@@ -1361,9 +1463,9 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
       <c r="D12" t="s">
         <v>38</v>
       </c>
@@ -1375,9 +1477,9 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
       <c r="D13" t="s">
         <v>40</v>
       </c>
@@ -1389,9 +1491,9 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
       <c r="D14" t="s">
         <v>42</v>
       </c>
@@ -1403,9 +1505,9 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
       <c r="D15" t="s">
         <v>43</v>
       </c>
@@ -1417,9 +1519,9 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
       <c r="D16" t="s">
         <v>46</v>
       </c>
@@ -1431,9 +1533,9 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
       <c r="D17" t="s">
         <v>48</v>
       </c>
@@ -1445,9 +1547,9 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
       <c r="D18" t="s">
         <v>49</v>
       </c>
@@ -1459,9 +1561,9 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
       <c r="D19" t="s">
         <v>51</v>
       </c>
@@ -1473,13 +1575,13 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" s="1" t="s">
+      <c r="A20" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="5" t="s">
         <v>81</v>
       </c>
       <c r="D20" t="s">
@@ -1493,9 +1595,9 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
       <c r="D21" t="s">
         <v>55</v>
       </c>
@@ -1507,9 +1609,9 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
       <c r="D22" t="s">
         <v>57</v>
       </c>
@@ -1521,9 +1623,9 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
+      <c r="A23" s="5"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
       <c r="D23" t="s">
         <v>59</v>
       </c>
@@ -1535,230 +1637,235 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B24" s="3" t="s">
+      <c r="A24" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
+      <c r="C24" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B25" s="3" t="s">
+      <c r="A25" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
+      <c r="C25" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D26" s="2" t="s">
+      <c r="A26" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="F26" s="1" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="2" t="s">
+      <c r="A27" s="5"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="F27" s="1" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="2" t="s">
+      <c r="A28" s="5"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E28" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="F28" s="2" t="s">
+      <c r="F28" s="1" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="A29" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="F29" s="1" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="A30" s="5"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="5"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F30" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E31" s="2" t="s">
+      <c r="F31" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="5"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E32" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F31" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F32" s="2" t="s">
+      <c r="F32" s="1" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="1"/>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>82</v>
-      </c>
+      <c r="A33" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>82</v>
-      </c>
+      <c r="A34" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>82</v>
+      <c r="A35" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="2"/>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
+      <c r="A36" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="2"/>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
+      <c r="A37" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>81</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="A32:A35"/>
-    <mergeCell ref="B32:B35"/>
-    <mergeCell ref="C32:C35"/>
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="B26:B28"/>
-    <mergeCell ref="C26:C28"/>
-    <mergeCell ref="A29:A31"/>
-    <mergeCell ref="B29:B31"/>
-    <mergeCell ref="C29:C31"/>
+  <mergeCells count="18">
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C5:C7"/>
     <mergeCell ref="A20:A23"/>
     <mergeCell ref="B20:B23"/>
     <mergeCell ref="C20:C23"/>
     <mergeCell ref="A8:A19"/>
     <mergeCell ref="B8:B19"/>
     <mergeCell ref="C8:C19"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="A29:A32"/>
+    <mergeCell ref="B29:B32"/>
+    <mergeCell ref="C29:C32"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="B26:B28"/>
+    <mergeCell ref="C26:C28"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/resource/专业分类.xlsx
+++ b/resource/专业分类.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25330"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\RustProject\aios_workspace\aios-database\resource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F389534-859C-4286-A17F-0C1E3B1E5473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1EFAE82-CBCA-4E10-89FC-00332F51A937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10660" yWindow="1090" windowWidth="11220" windowHeight="14230" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="97">
   <si>
     <t>PIPE</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -412,46 +412,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>F</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>辐射安全</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>H</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>反应堆热工水力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>R</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>辐射监测</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>建筑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>J</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>结构</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>N</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -461,14 +421,6 @@
   </si>
   <si>
     <t>给排水</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>L</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>照明</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1669,7 +1621,7 @@
         <v>89</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>81</v>
@@ -1714,10 +1666,10 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>81</v>
@@ -1775,97 +1727,61 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>81</v>
-      </c>
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="3"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>81</v>
-      </c>
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="3"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>81</v>
-      </c>
+      <c r="A35" s="4"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="3"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>81</v>
-      </c>
+      <c r="A36" s="4"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="3"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>81</v>
-      </c>
+      <c r="A37" s="4"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="3"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>81</v>
-      </c>
+      <c r="A38" s="4"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A29:A32"/>
+    <mergeCell ref="B29:B32"/>
+    <mergeCell ref="C29:C32"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="B26:B28"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="B20:B23"/>
+    <mergeCell ref="C20:C23"/>
+    <mergeCell ref="A8:A19"/>
+    <mergeCell ref="B8:B19"/>
+    <mergeCell ref="C8:C19"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="C2:C4"/>
     <mergeCell ref="A5:A7"/>
     <mergeCell ref="B5:B7"/>
     <mergeCell ref="C5:C7"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="B20:B23"/>
-    <mergeCell ref="C20:C23"/>
-    <mergeCell ref="A8:A19"/>
-    <mergeCell ref="B8:B19"/>
-    <mergeCell ref="C8:C19"/>
-    <mergeCell ref="A29:A32"/>
-    <mergeCell ref="B29:B32"/>
-    <mergeCell ref="C29:C32"/>
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="B26:B28"/>
-    <mergeCell ref="C26:C28"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/resource/专业分类.xlsx
+++ b/resource/专业分类.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\RustProject\aios_workspace\aios-database\resource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1EFAE82-CBCA-4E10-89FC-00332F51A937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5637285-FD86-4465-AD21-15F7C8861E7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10660" yWindow="1090" windowWidth="11220" windowHeight="14230" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="98">
   <si>
     <t>PIPE</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -416,11 +416,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>暖通</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>给排水</t>
+    <t>通信布置专业</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>给排水布置专业</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暖通布置专业</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1593,7 +1597,7 @@
         <v>92</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>9</v>
+        <v>95</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>81</v>
@@ -1669,7 +1673,7 @@
         <v>94</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>81</v>
@@ -1764,26 +1768,27 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="B20:B23"/>
+    <mergeCell ref="C20:C23"/>
+    <mergeCell ref="A8:A19"/>
+    <mergeCell ref="B8:B19"/>
+    <mergeCell ref="C8:C19"/>
     <mergeCell ref="A29:A32"/>
     <mergeCell ref="B29:B32"/>
     <mergeCell ref="C29:C32"/>
     <mergeCell ref="A26:A28"/>
     <mergeCell ref="B26:B28"/>
     <mergeCell ref="C26:C28"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="B20:B23"/>
-    <mergeCell ref="C20:C23"/>
-    <mergeCell ref="A8:A19"/>
-    <mergeCell ref="B8:B19"/>
-    <mergeCell ref="C8:C19"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="C5:C7"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
 </worksheet>
 </file>
--- a/resource/专业分类.xlsx
+++ b/resource/专业分类.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\RustProject\aios_workspace\aios-database\resource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5637285-FD86-4465-AD21-15F7C8861E7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06E3014F-4575-43D0-AC43-F262ABB3E572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="101">
   <si>
     <t>PIPE</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -420,11 +420,59 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>给排水布置专业</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>暖通布置专业</t>
+    <r>
+      <t>BOP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>部分</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>水工</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>BOPWP</t>
+  </si>
+  <si>
+    <t>BOPWSU</t>
+  </si>
+  <si>
+    <t>BOPWE</t>
+  </si>
+  <si>
+    <t>Z</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -432,7 +480,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -446,6 +494,25 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -468,7 +535,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -477,12 +544,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1231,7 +1302,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CE6209C-C647-4AE3-9980-4524CAC659D9}">
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.5" customWidth="1"/>
@@ -1593,62 +1664,68 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C24" s="2" t="s">
+      <c r="A24" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
+      <c r="D24" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="2" t="s">
+      <c r="A25" s="5"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="5"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="5"/>
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
       <c r="D27" s="1" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>82</v>
@@ -1659,30 +1736,24 @@
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
       <c r="D28" s="1" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>81</v>
-      </c>
+      <c r="A29" s="5"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
       <c r="D29" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>82</v>
@@ -1693,24 +1764,30 @@
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
       <c r="D30" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="5"/>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="1" t="s">
-        <v>77</v>
+    <row r="31" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>97</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>82</v>
@@ -1718,74 +1795,88 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="5"/>
-      <c r="B32" s="5"/>
+      <c r="B32" s="7"/>
       <c r="C32" s="5"/>
-      <c r="D32" s="1" t="s">
-        <v>73</v>
+      <c r="D32" s="6" t="s">
+        <v>98</v>
       </c>
       <c r="E32" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="5"/>
+      <c r="B33" s="7"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F32" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
+      <c r="F33" s="1" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="3"/>
+      <c r="A34" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>81</v>
+      </c>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="4"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="3"/>
+      <c r="A35" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="4"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="3"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="4"/>
-      <c r="B37" s="4"/>
-      <c r="C37" s="3"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="4"/>
-      <c r="B38" s="4"/>
-      <c r="C38" s="3"/>
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="21">
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="C31:C33"/>
+    <mergeCell ref="A31:A33"/>
+    <mergeCell ref="A27:A30"/>
+    <mergeCell ref="B27:B30"/>
+    <mergeCell ref="C27:C30"/>
+    <mergeCell ref="A24:A26"/>
+    <mergeCell ref="B24:B26"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="B20:B23"/>
+    <mergeCell ref="C20:C23"/>
+    <mergeCell ref="A8:A19"/>
+    <mergeCell ref="B8:B19"/>
+    <mergeCell ref="C8:C19"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="C2:C4"/>
     <mergeCell ref="A5:A7"/>
     <mergeCell ref="B5:B7"/>
     <mergeCell ref="C5:C7"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="B20:B23"/>
-    <mergeCell ref="C20:C23"/>
-    <mergeCell ref="A8:A19"/>
-    <mergeCell ref="B8:B19"/>
-    <mergeCell ref="C8:C19"/>
-    <mergeCell ref="A29:A32"/>
-    <mergeCell ref="B29:B32"/>
-    <mergeCell ref="C29:C32"/>
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="B26:B28"/>
-    <mergeCell ref="C26:C28"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/resource/专业分类.xlsx
+++ b/resource/专业分类.xlsx
@@ -4,18 +4,31 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12330" activeTab="1"/>
+    <workbookView windowWidth="25600" windowHeight="12200" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="127">
   <si>
     <t>code</t>
   </si>
@@ -338,69 +351,61 @@
     <t>RACK</t>
   </si>
   <si>
+    <t>-EQUI</t>
+  </si>
+  <si>
+    <t>YK</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>BOP</t>
+  </si>
+  <si>
     <t>W</t>
   </si>
   <si>
-    <t>PIPE-F</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>BOP</t>
-  </si>
-  <si>
-    <t>Z</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>BOP</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>部分</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>水工</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <t>SG</t>
+    <t>FWD-PIPE</t>
+  </si>
+  <si>
+    <t>FNP-PIPE</t>
+  </si>
+  <si>
+    <t>FGP-PIPE</t>
+  </si>
+  <si>
+    <t>FSP-PIPE</t>
+  </si>
+  <si>
+    <t>FEP-PIPE</t>
+  </si>
+  <si>
+    <t>FDP-PIPE</t>
+  </si>
+  <si>
+    <t>FWP-PIPE</t>
+  </si>
+  <si>
+    <t>WSS-PIPE</t>
+  </si>
+  <si>
+    <t>WRC-PIPE</t>
+  </si>
+  <si>
+    <t>WOD-PIPE</t>
+  </si>
+  <si>
+    <t>WPW-PIPE</t>
+  </si>
+  <si>
+    <t>HDY-PIPE</t>
+  </si>
+  <si>
+    <t>WWS-PIPE</t>
+  </si>
+  <si>
+    <t>WSW-PIPE</t>
   </si>
   <si>
     <t>END</t>
@@ -409,14 +414,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -425,44 +430,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -478,14 +449,6 @@
       <color rgb="FF800080"/>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -525,6 +488,21 @@
       <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -575,16 +553,31 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
@@ -596,55 +589,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -662,31 +613,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -710,6 +649,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -722,7 +673,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -746,7 +721,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -770,6 +757,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -787,21 +780,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -834,6 +812,21 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -890,152 +883,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1046,58 +1039,58 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1835,7 +1828,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="18.5" customWidth="1"/>
@@ -2445,81 +2438,81 @@
       </c>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="4" t="s">
         <v>107</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H24" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>88</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -2536,16 +2529,16 @@
         <v>110</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>3</v>
+        <v>88</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -2562,187 +2555,1135 @@
         <v>110</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1" spans="1:8">
       <c r="A29" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D29" s="1" t="s">
-        <v>110</v>
+      <c r="D29" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>88</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D30" s="1" t="s">
-        <v>110</v>
+      <c r="D30" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H30" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H31" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="31" ht="16" customHeight="1" spans="1:8">
-      <c r="A31" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D31" s="4" t="s">
+    <row r="32" spans="1:8">
+      <c r="A32" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="E31" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H31" s="1" t="s">
+      <c r="E32" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H32" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="32" ht="15.5" spans="1:8">
-      <c r="A32" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D32" s="4" t="s">
+    <row r="33" spans="1:8">
+      <c r="A33" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="E32" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H32" s="1" t="s">
+      <c r="E33" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H33" s="1" t="s">
         <v>88</v>
-      </c>
-    </row>
-    <row r="33" ht="15.5" spans="1:8">
-      <c r="A33" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="E35" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D36" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="E36" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D34" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="2"/>
-      <c r="B36" s="2"/>
-      <c r="C36" s="1"/>
+      <c r="E37" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>126</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
